--- a/2026/ЗАВОДЫ/Останкино/филиалы НВ/10,26/05,10,26 Останкино КИ и ЗПФ/машины Останкино КИ и ЗПФ.xlsx
+++ b/2026/ЗАВОДЫ/Останкино/филиалы НВ/10,26/05,10,26 Останкино КИ и ЗПФ/машины Останкино КИ и ЗПФ.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты Останкино КИ и ЗПФ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\2026\ЗАВОДЫ\Останкино\филиалы НВ\10,26\05,10,26 Останкино КИ и ЗПФ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29C9C20D-CD73-48D6-A9EF-A8E61F2CE5BE}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B32E6650-AA63-4BE6-8129-AA736CC8F105}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -145,7 +145,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -170,6 +170,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="6">
     <border>
@@ -256,7 +262,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -276,6 +282,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -669,7 +676,7 @@
       </c>
       <c r="C6" s="6"/>
       <c r="D6" s="6"/>
-      <c r="E6" s="6">
+      <c r="E6" s="13">
         <v>2729</v>
       </c>
       <c r="F6" s="6">
@@ -689,7 +696,7 @@
       </c>
       <c r="C7" s="6"/>
       <c r="D7" s="6"/>
-      <c r="E7" s="6">
+      <c r="E7" s="13">
         <v>90</v>
       </c>
       <c r="F7" s="6">
